--- a/EX_3_1.xlsx
+++ b/EX_3_1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Product\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Product_AMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C11E0D2-E542-4140-8542-70F6CA2A6F2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C50488-611B-4333-9421-AB2EB866C739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6A9E45DC-C312-4E47-9FEB-1FF5EFDB5A84}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{6A9E45DC-C312-4E47-9FEB-1FF5EFDB5A84}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -131,10 +131,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -592,7 +592,7 @@
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
@@ -621,7 +621,7 @@
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
+      <c r="A3" s="2"/>
       <c r="B3" t="s">
         <v>2</v>
       </c>
@@ -648,7 +648,7 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B4" t="s">
@@ -677,7 +677,7 @@
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
+      <c r="A5" s="2"/>
       <c r="B5" t="s">
         <v>2</v>
       </c>
@@ -816,7 +816,7 @@
       <c r="G14">
         <v>5</v>
       </c>
-      <c r="L14" s="1" t="s">
+      <c r="L14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="M14" t="s">
@@ -844,7 +844,7 @@
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B15" t="s">
@@ -870,7 +870,7 @@
         <f t="shared" si="2"/>
         <v>30000</v>
       </c>
-      <c r="L15" s="1"/>
+      <c r="L15" s="2"/>
       <c r="M15" t="s">
         <v>2</v>
       </c>
@@ -896,7 +896,7 @@
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
+      <c r="A16" s="2"/>
       <c r="B16" t="s">
         <v>2</v>
       </c>
@@ -920,7 +920,7 @@
         <f t="shared" si="4"/>
         <v>6750</v>
       </c>
-      <c r="L16" s="1" t="s">
+      <c r="L16" s="2" t="s">
         <v>11</v>
       </c>
       <c r="M16" t="s">
@@ -948,7 +948,7 @@
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B17" t="s">
@@ -974,7 +974,7 @@
         <f t="shared" si="5"/>
         <v>25000</v>
       </c>
-      <c r="L17" s="1"/>
+      <c r="L17" s="2"/>
       <c r="M17" t="s">
         <v>2</v>
       </c>
@@ -1000,7 +1000,7 @@
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
+      <c r="A18" s="2"/>
       <c r="B18" t="s">
         <v>2</v>
       </c>
@@ -1100,7 +1100,7 @@
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+      <c r="A20" s="1">
         <v>0.1</v>
       </c>
       <c r="C20">
@@ -1126,7 +1126,7 @@
       <c r="H20" t="s">
         <v>13</v>
       </c>
-      <c r="L20" s="2">
+      <c r="L20" s="1">
         <v>0.1</v>
       </c>
       <c r="M20" t="s">
@@ -1154,7 +1154,7 @@
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+      <c r="A21" s="1">
         <v>0.8</v>
       </c>
       <c r="C21">
@@ -1205,7 +1205,7 @@
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="L22" s="2">
+      <c r="L22" s="1">
         <v>0.9</v>
       </c>
       <c r="M22" t="s">
@@ -1456,6 +1456,15 @@
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="E29">
+        <v>3</v>
+      </c>
+      <c r="F29">
+        <v>4</v>
+      </c>
+      <c r="G29">
+        <v>3</v>
+      </c>
       <c r="L29" t="s">
         <v>18</v>
       </c>
